--- a/docs/vykaz_studenta_k_projektom_programko_stranka.xlsx
+++ b/docs/vykaz_studenta_k_projektom_programko_stranka.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>PRACOVNÝ VÝKAZ ŽIAKA</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>Zmena grafickeho dizajnu + upgrade dashboardu a article systemu</t>
+  </si>
+  <si>
+    <t>Pridanie markdown supportu pre články, podpora úpravi článkov non admin autormi</t>
+  </si>
+  <si>
+    <t>Úprava manažovania článkov v časti pre použivatelov a pridanie profilu a uprava profilu</t>
   </si>
 </sst>
 </file>
@@ -1230,8 +1236,12 @@
       <c r="C17" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="26"/>
-      <c r="E17" s="31"/>
+      <c r="D17" s="26">
+        <v>90</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>24</v>
+      </c>
       <c r="F17" s="31"/>
       <c r="G17" s="31"/>
       <c r="H17" s="31"/>
@@ -1242,10 +1252,18 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="1"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="34"/>
+      <c r="B18" s="24">
+        <v>46174</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="26">
+        <v>90</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>25</v>
+      </c>
       <c r="F18" s="35"/>
       <c r="G18" s="35"/>
       <c r="H18" s="35"/>

--- a/docs/vykaz_studenta_k_projektom_programko_stranka.xlsx
+++ b/docs/vykaz_studenta_k_projektom_programko_stranka.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>PRACOVNÝ VÝKAZ ŽIAKA</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>Úprava manažovania článkov v časti pre použivatelov a pridanie profilu a uprava profilu</t>
+  </si>
+  <si>
+    <t>Uprava Autorov v articloch pridanie front page banner nastavenia</t>
   </si>
 </sst>
 </file>
@@ -1274,10 +1277,18 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="34"/>
+      <c r="B19" s="24">
+        <v>46177</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="26">
+        <v>60</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>26</v>
+      </c>
       <c r="F19" s="35"/>
       <c r="G19" s="35"/>
       <c r="H19" s="35"/>
@@ -1342,7 +1353,7 @@
       <c r="K23" s="35"/>
       <c r="L23" s="37"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="1"/>
       <c r="B24" s="24"/>
       <c r="C24" s="25"/>
@@ -1356,7 +1367,7 @@
       <c r="K24" s="35"/>
       <c r="L24" s="37"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20.25">
       <c r="A25" s="1"/>
       <c r="B25" s="38"/>
       <c r="C25" s="39"/>
@@ -1370,7 +1381,7 @@
       <c r="K25" s="42"/>
       <c r="L25" s="44"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20.25">
       <c r="A26" s="1"/>
       <c r="B26" s="2"/>
       <c r="C26" s="3"/>
@@ -1384,7 +1395,7 @@
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="1"/>
       <c r="B27" s="2"/>
       <c r="C27" s="3"/>

--- a/docs/vykaz_studenta_k_projektom_programko_stranka.xlsx
+++ b/docs/vykaz_studenta_k_projektom_programko_stranka.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
   <si>
     <t>PRACOVNÝ VÝKAZ ŽIAKA</t>
   </si>
@@ -117,6 +117,12 @@
   </si>
   <si>
     <t>Uprava Autorov v articloch pridanie front page banner nastavenia</t>
+  </si>
+  <si>
+    <t>domov</t>
+  </si>
+  <si>
+    <t>Bug fixi a security update</t>
   </si>
 </sst>
 </file>
@@ -1299,10 +1305,18 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="1"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="34"/>
+      <c r="B20" s="24">
+        <v>46180</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="26">
+        <v>30</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>28</v>
+      </c>
       <c r="F20" s="35"/>
       <c r="G20" s="35"/>
       <c r="H20" s="35"/>

--- a/docs/vykaz_studenta_k_projektom_programko_stranka.xlsx
+++ b/docs/vykaz_studenta_k_projektom_programko_stranka.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="30">
   <si>
     <t>PRACOVNÝ VÝKAZ ŽIAKA</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>Bug fixi a security update</t>
+  </si>
+  <si>
+    <t>Bug fixi, clean up a commentare ui/ux uprava</t>
   </si>
 </sst>
 </file>
@@ -1327,10 +1330,18 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="1"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="34"/>
+      <c r="B21" s="24">
+        <v>46181</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="26">
+        <v>90</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>29</v>
+      </c>
       <c r="F21" s="35"/>
       <c r="G21" s="35"/>
       <c r="H21" s="35"/>

--- a/docs/vykaz_studenta_k_projektom_programko_stranka.xlsx
+++ b/docs/vykaz_studenta_k_projektom_programko_stranka.xlsx
@@ -1,15 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zochova-my.sharepoint.com/personal/tadeasnevrela_s_zochova_sk/Documents/Dokumenty/GitHub/Quack_wiki/docs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_F4C063202D6A2B914D14B228FB4A8FCE9D4E7F44" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{054CFF8F-9844-4B94-994A-26F7B8AE5BF8}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Hárok1"/>
+    <sheet name="Hárok1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -67,7 +86,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFffffff"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
       </rPr>
@@ -81,7 +100,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFffffff"/>
+        <color rgb="FFFFFFFF"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
       </rPr>
@@ -125,15 +144,14 @@
     <t>Bug fixi a security update</t>
   </si>
   <si>
-    <t>Bug fixi, clean up a commentare ui/ux uprava</t>
+    <t>Bug fixi, clean up a commentare ui/ux uprava permission update + article edit update + search by tags</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,21 +175,27 @@
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
-      <color rgb="FF3b7d23"/>
+      <color rgb="FF3B7D23"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFffffff"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -209,34 +233,34 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="medium">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="medium">
         <color rgb="FF000000"/>
@@ -245,7 +269,7 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
       <diagonal/>
     </border>
@@ -302,7 +326,7 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -314,10 +338,10 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
@@ -329,7 +353,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFc6c6c6"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="medium">
         <color rgb="FF000000"/>
@@ -465,161 +489,167 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+  <cellXfs count="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="4" applyBorder="1" fontId="3" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="6" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="5" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="5" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="5" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="5" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="9" applyBorder="1" fontId="5" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="10" applyBorder="1" fontId="5" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="10" applyBorder="1" fontId="5" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="11" applyBorder="1" fontId="5" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="7" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="13" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="14" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="8" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="15" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="12" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="13" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="13" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="14" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="16" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="17" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="17" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="18" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="19" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="19" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="20" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="14" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normálna" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -630,10 +660,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -671,71 +701,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -763,7 +793,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -786,11 +816,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -799,13 +829,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -815,7 +845,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -824,7 +854,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -833,7 +863,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -841,10 +871,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -909,640 +939,607 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:L33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="45" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="46" width="14.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="47" width="12.719285714285713" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="48" width="11.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="47" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="47" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="47" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="47" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="47" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="48" width="10.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="47" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="47" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="13.5703125" style="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" style="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.5703125" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="25.5">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6" t="s">
+    <row r="1" spans="1:12" ht="19.5" customHeight="1">
+      <c r="B1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:12" ht="25.5" customHeight="1">
+      <c r="A2" s="4"/>
+      <c r="B2" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="9"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="10"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="12"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="13"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="12"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="13"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="24.75">
-      <c r="A5" s="1"/>
-      <c r="B5" s="11" t="s">
+      <c r="C2" s="25"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="27"/>
+    </row>
+    <row r="3" spans="1:12" ht="18.75" customHeight="1">
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="8"/>
+    </row>
+    <row r="4" spans="1:12" ht="18.75" customHeight="1">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" spans="1:12" ht="24.75" customHeight="1">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="5" t="s">
+      <c r="D5" s="29"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="14">
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="9">
         <f>SUM(D:D)</f>
-      </c>
-      <c r="K5" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="15"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="24.75">
-      <c r="A6" s="1"/>
-      <c r="B6" s="11" t="s">
+      <c r="L5" s="10"/>
+    </row>
+    <row r="6" spans="1:12" ht="24.75" customHeight="1">
+      <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="5" t="s">
+      <c r="D6" s="29"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="14">
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="9">
         <f>COUNT(B11:B35)</f>
-      </c>
-      <c r="K6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="15"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="1"/>
-      <c r="B7" s="11" t="s">
+      <c r="L6" s="10"/>
+    </row>
+    <row r="7" spans="1:12" ht="19.5" customHeight="1">
+      <c r="B7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="15"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="1"/>
-      <c r="B8" s="11" t="s">
+      <c r="D7" s="29"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="10"/>
+    </row>
+    <row r="8" spans="1:12" ht="19.5" customHeight="1">
+      <c r="B8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="15"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="1"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="15"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="1"/>
-      <c r="B10" s="17" t="s">
+      <c r="D8" s="29"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" spans="1:12" ht="18.75" customHeight="1">
+      <c r="B9" s="11"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="10"/>
+    </row>
+    <row r="10" spans="1:12" ht="18.75" customHeight="1">
+      <c r="B10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="23"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="1"/>
-      <c r="B11" s="24">
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="34"/>
+    </row>
+    <row r="11" spans="1:12" ht="19.5" customHeight="1">
+      <c r="B11" s="15">
         <v>46128</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="17">
         <v>45</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="28"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="30"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="1"/>
-      <c r="B12" s="24">
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="38"/>
+    </row>
+    <row r="12" spans="1:12" ht="19.5" customHeight="1">
+      <c r="B12" s="15">
         <v>46136</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="17">
         <v>90</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="31"/>
-      <c r="L12" s="33"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="1"/>
-      <c r="B13" s="24">
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="41"/>
+    </row>
+    <row r="13" spans="1:12" ht="19.5" customHeight="1">
+      <c r="B13" s="15">
         <v>46139</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="17">
         <v>180</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="33"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="1"/>
-      <c r="B14" s="24">
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="41"/>
+    </row>
+    <row r="14" spans="1:12" ht="19.5" customHeight="1">
+      <c r="B14" s="15">
         <v>46142</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="17">
         <v>90</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="33"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="1"/>
-      <c r="B15" s="24">
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="41"/>
+    </row>
+    <row r="15" spans="1:12" ht="19.5" customHeight="1">
+      <c r="B15" s="15">
         <v>46149</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="17">
         <v>45</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="33"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="1"/>
-      <c r="B16" s="24">
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="39"/>
+      <c r="L15" s="41"/>
+    </row>
+    <row r="16" spans="1:12" ht="19.5" customHeight="1">
+      <c r="B16" s="15">
         <v>46167</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="17">
         <v>180</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="33"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="1"/>
-      <c r="B17" s="24">
+      <c r="F16" s="39"/>
+      <c r="G16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="39"/>
+      <c r="L16" s="41"/>
+    </row>
+    <row r="17" spans="2:12" ht="19.5" customHeight="1">
+      <c r="B17" s="15">
         <v>46170</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="17">
         <v>90</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="33"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="1"/>
-      <c r="B18" s="24">
+      <c r="F17" s="39"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="39"/>
+      <c r="L17" s="41"/>
+    </row>
+    <row r="18" spans="2:12" ht="19.5" customHeight="1">
+      <c r="B18" s="15">
         <v>46174</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D18" s="26">
+      <c r="D18" s="17">
         <v>90</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="35"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="35"/>
-      <c r="L18" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="1"/>
-      <c r="B19" s="24">
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="44"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="45"/>
+    </row>
+    <row r="19" spans="2:12" ht="19.5" customHeight="1">
+      <c r="B19" s="15">
         <v>46177</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="17">
         <v>60</v>
       </c>
-      <c r="E19" s="34" t="s">
+      <c r="E19" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="35"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="35"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="35"/>
-      <c r="L19" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="1"/>
-      <c r="B20" s="24">
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="45"/>
+    </row>
+    <row r="20" spans="2:12" ht="19.5" customHeight="1">
+      <c r="B20" s="15">
         <v>46180</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="17">
         <v>30</v>
       </c>
-      <c r="E20" s="34" t="s">
+      <c r="E20" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
-      <c r="A21" s="1"/>
-      <c r="B21" s="24">
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="45"/>
+    </row>
+    <row r="21" spans="2:12" ht="19.5" customHeight="1">
+      <c r="B21" s="15">
         <v>46181</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D21" s="26">
-        <v>90</v>
-      </c>
-      <c r="E21" s="34" t="s">
+      <c r="D21" s="17">
+        <v>150</v>
+      </c>
+      <c r="E21" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="35"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="35"/>
-      <c r="L21" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
-      <c r="A22" s="1"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
-      <c r="A23" s="1"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
-      <c r="A24" s="1"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="35"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="35"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="35"/>
-      <c r="L24" s="37"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="20.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="44"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="20.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
-      <c r="A27" s="1"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="1"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="1"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="1"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="1"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="1"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="1"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="45"/>
+    </row>
+    <row r="22" spans="2:12" ht="19.5" customHeight="1">
+      <c r="B22" s="15"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="45"/>
+    </row>
+    <row r="23" spans="2:12" ht="19.5" customHeight="1">
+      <c r="B23" s="15"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="43"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="45"/>
+    </row>
+    <row r="24" spans="2:12" ht="19.5" customHeight="1">
+      <c r="B24" s="15"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="43"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="45"/>
+    </row>
+    <row r="25" spans="2:12" ht="20.25" customHeight="1">
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="47"/>
+      <c r="I25" s="47"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="47"/>
+      <c r="L25" s="49"/>
+    </row>
+    <row r="26" spans="2:12" ht="20.25" customHeight="1">
+      <c r="B26" s="1"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" spans="2:12" ht="19.5" customHeight="1">
+      <c r="B27" s="1"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" customHeight="1">
+      <c r="B28" s="1"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="2:12" ht="18.75" customHeight="1">
+      <c r="B29" s="1"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" spans="2:12" ht="18.75" customHeight="1">
+      <c r="B30" s="1"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" spans="2:12" ht="18.75" customHeight="1">
+      <c r="B31" s="1"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="2:12" ht="18.75" customHeight="1">
+      <c r="B32" s="1"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" spans="2:12" ht="18.75" customHeight="1">
+      <c r="B33" s="1"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="E23:L23"/>
+    <mergeCell ref="E24:L24"/>
+    <mergeCell ref="E25:L25"/>
+    <mergeCell ref="E18:L18"/>
+    <mergeCell ref="E19:L19"/>
+    <mergeCell ref="E20:L20"/>
+    <mergeCell ref="E21:L21"/>
+    <mergeCell ref="E22:L22"/>
+    <mergeCell ref="E13:L13"/>
+    <mergeCell ref="E14:L14"/>
+    <mergeCell ref="E15:L15"/>
+    <mergeCell ref="E16:L16"/>
+    <mergeCell ref="E17:L17"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:K8"/>
+    <mergeCell ref="E10:L10"/>
+    <mergeCell ref="E11:L11"/>
+    <mergeCell ref="E12:L12"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="F5:I5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="F6:I6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:K8"/>
-    <mergeCell ref="E10:L10"/>
-    <mergeCell ref="E11:L11"/>
-    <mergeCell ref="E12:L12"/>
-    <mergeCell ref="E13:L13"/>
-    <mergeCell ref="E14:L14"/>
-    <mergeCell ref="E15:L15"/>
-    <mergeCell ref="E16:L16"/>
-    <mergeCell ref="E17:L17"/>
-    <mergeCell ref="E18:L18"/>
-    <mergeCell ref="E19:L19"/>
-    <mergeCell ref="E20:L20"/>
-    <mergeCell ref="E21:L21"/>
-    <mergeCell ref="E22:L22"/>
-    <mergeCell ref="E23:L23"/>
-    <mergeCell ref="E24:L24"/>
-    <mergeCell ref="E25:L25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
